--- a/data/trans_dic/P1403-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1403-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -722,22 +722,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,21</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,5</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,88</t>
+          <t>0,1; 0,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,43</t>
+          <t>0,13; 2,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,89</t>
+          <t>0,41; 2,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,45</t>
+          <t>0,45; 2,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,57</t>
+          <t>0,83; 4,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,74</t>
+          <t>0,77; 2,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,04</t>
+          <t>0,66; 2,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,23</t>
+          <t>0,37; 2,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,4</t>
+          <t>0,44; 1,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,05</t>
+          <t>0,71; 2,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,51</t>
+          <t>0,38; 1,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,8</t>
+          <t>0,74; 2,76</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,65</t>
+          <t>1,99; 4,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,68</t>
+          <t>3,38; 7,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,07</t>
+          <t>2,24; 5,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,69</t>
+          <t>2,39; 5,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,15</t>
+          <t>3,06; 6,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,15</t>
+          <t>2,29; 5,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,85</t>
+          <t>1,51; 4,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,76</t>
+          <t>1,47; 3,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,97</t>
+          <t>2,85; 4,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,5</t>
+          <t>3,3; 5,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,1</t>
+          <t>2,17; 4,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,24</t>
+          <t>2,19; 4,17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 17,22</t>
+          <t>11,07; 17,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 14,67</t>
+          <t>9,36; 14,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 16,93</t>
+          <t>10,59; 16,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 17,76</t>
+          <t>13,6; 19,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 14,01</t>
+          <t>8,4; 14,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,52</t>
+          <t>10,93; 16,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 11,31</t>
+          <t>6,96; 11,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 15,6</t>
+          <t>10,61; 14,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 14,66</t>
+          <t>10,55; 14,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 14,71</t>
+          <t>10,89; 14,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 13,33</t>
+          <t>9,5; 13,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 15,5</t>
+          <t>12,56; 16,14</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,4; 35,74</t>
+          <t>26,38; 36,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,68; 40,33</t>
+          <t>30,18; 40,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,91; 29,48</t>
+          <t>21,11; 29,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,86; 33,17</t>
+          <t>25,48; 32,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,09; 35,9</t>
+          <t>26,98; 36,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,46; 43,96</t>
+          <t>34,07; 43,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,23; 34,12</t>
+          <t>25,7; 33,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,69; 29,36</t>
+          <t>24,05; 29,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,8; 34,28</t>
+          <t>27,97; 34,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33,79; 40,64</t>
+          <t>33,67; 40,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,66; 30,62</t>
+          <t>24,51; 30,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,76; 30,53</t>
+          <t>25,45; 29,83</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,0; 44,8</t>
+          <t>33,09; 44,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,14; 58,2</t>
+          <t>46,02; 58,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,02; 46,16</t>
+          <t>35,61; 46,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42,09; 50,76</t>
+          <t>41,41; 49,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,29; 51,07</t>
+          <t>40,43; 50,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,93; 62,79</t>
+          <t>52,27; 62,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,99; 51,61</t>
+          <t>41,22; 52,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,47; 86,48</t>
+          <t>43,47; 50,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,7; 46,27</t>
+          <t>38,93; 46,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50,79; 58,66</t>
+          <t>50,75; 58,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40,13; 47,55</t>
+          <t>39,99; 47,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,41; 78,8</t>
+          <t>43,76; 49,29</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,12%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,12; 55,07</t>
+          <t>39,71; 53,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,94; 66,23</t>
+          <t>54,12; 67,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,53; 59,51</t>
+          <t>48,17; 59,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,69; 58,99</t>
+          <t>49,91; 58,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,09; 62,32</t>
+          <t>50,56; 62,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,6; 69,43</t>
+          <t>60,04; 69,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,25; 62,46</t>
+          <t>51,24; 62,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>61,16; 67,94</t>
+          <t>60,41; 67,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,43; 57,37</t>
+          <t>48,4; 57,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,24; 67,06</t>
+          <t>59,17; 67,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51,71; 59,91</t>
+          <t>51,94; 59,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,66; 63,4</t>
+          <t>57,49; 62,87</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,96; 14,33</t>
+          <t>11,93; 14,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,45; 18,06</t>
+          <t>15,5; 18,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,95; 16,36</t>
+          <t>13,84; 16,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,0; 19,94</t>
+          <t>17,94; 20,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,77; 18,24</t>
+          <t>15,79; 18,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,46; 22,29</t>
+          <t>19,56; 22,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,45; 19,08</t>
+          <t>16,45; 19,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,3; 40,41</t>
+          <t>19,86; 22,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,25; 15,91</t>
+          <t>14,04; 15,83</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,81</t>
+          <t>17,99; 19,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,52; 17,32</t>
+          <t>15,61; 17,51</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,79; 29,88</t>
+          <t>19,27; 20,9</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>5886</t>
         </is>
       </c>
     </row>
@@ -2068,27 +2068,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3929</t>
+          <t>0; 3963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4825</t>
+          <t>0; 4298</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6862</t>
+          <t>0; 6980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 853</t>
+          <t>0; 14438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>783; 7022</t>
+          <t>0; 7560</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2098,32 +2098,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4524</t>
+          <t>0; 4525</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9516</t>
+          <t>0; 11137</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>929; 8461</t>
+          <t>935; 9489</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4503</t>
+          <t>0; 4830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 8318</t>
+          <t>0; 8314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>554; 10201</t>
+          <t>1021; 17612</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>14474</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7152</t>
+          <t>0; 6482</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2774; 12990</t>
+          <t>2837; 13783</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2758; 14481</t>
+          <t>2640; 15743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1527; 10875</t>
+          <t>3956; 20931</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4849; 17125</t>
+          <t>4811; 16922</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4710; 18536</t>
+          <t>4040; 18033</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6671</t>
+          <t>0; 6406</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1504; 11416</t>
+          <t>1844; 11282</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5312; 19025</t>
+          <t>5988; 20291</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9382; 26631</t>
+          <t>9263; 26331</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3944; 17435</t>
+          <t>4443; 18238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4420; 16821</t>
+          <t>7285; 26996</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>37934</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12698; 29683</t>
+          <t>12713; 30951</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22404; 45565</t>
+          <t>23058; 48220</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14584; 33913</t>
+          <t>14989; 35440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12447; 30451</t>
+          <t>14781; 36798</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20838; 42400</t>
+          <t>21076; 44065</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16772; 36549</t>
+          <t>16237; 36904</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9685; 25488</t>
+          <t>9965; 26554</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8435; 20361</t>
+          <t>9121; 21360</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39014; 66041</t>
+          <t>37901; 66114</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44924; 76544</t>
+          <t>45868; 78905</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29273; 54510</t>
+          <t>28864; 53325</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23043; 45698</t>
+          <t>27119; 51707</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107153</t>
+          <t>112212</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90785</t>
+          <t>93512</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>197938</t>
+          <t>205724</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55838; 89382</t>
+          <t>57462; 89006</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56244; 90161</t>
+          <t>57500; 90868</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71518; 109406</t>
+          <t>68430; 105020</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47351; 157714</t>
+          <t>95283; 134488</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43640; 72227</t>
+          <t>43331; 72416</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66351; 101470</t>
+          <t>67133; 103086</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44949; 73425</t>
+          <t>45202; 75497</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>74551; 111179</t>
+          <t>78174; 107507</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>109750; 151698</t>
+          <t>109204; 152523</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>133252; 180814</t>
+          <t>133800; 182624</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123777; 172619</t>
+          <t>122997; 170647</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>124341; 248081</t>
+          <t>180535; 232009</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165505</t>
+          <t>174194</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>142973</t>
+          <t>162260</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>308478</t>
+          <t>336454</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>102100; 138218</t>
+          <t>102021; 139385</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>131755; 173181</t>
+          <t>129614; 172174</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99945; 140878</t>
+          <t>100880; 141583</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144872; 185847</t>
+          <t>155022; 196377</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>109438; 145047</t>
+          <t>109010; 146070</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>154323; 196831</t>
+          <t>152547; 196725</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>125356; 169506</t>
+          <t>127678; 168748</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>128920; 159729</t>
+          <t>145782; 179922</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>219797; 271081</t>
+          <t>221180; 271881</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>296394; 356481</t>
+          <t>295336; 356319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>240351; 298425</t>
+          <t>238962; 297204</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>284496; 337185</t>
+          <t>309104; 362329</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169863</t>
+          <t>184926</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>391476</t>
+          <t>205743</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>561340</t>
+          <t>390669</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>99490; 131071</t>
+          <t>96830; 129678</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>142944; 180288</t>
+          <t>142566; 180148</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>120433; 154331</t>
+          <t>119062; 153826</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>154093; 185824</t>
+          <t>167560; 201999</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>141598; 175132</t>
+          <t>138664; 173976</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>183827; 222289</t>
+          <t>185024; 222230</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>154862; 194956</t>
+          <t>155700; 196817</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>276067; 525104</t>
+          <t>190387; 221553</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>245920; 294054</t>
+          <t>247380; 295645</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>337162; 389380</t>
+          <t>336856; 390488</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>285758; 338574</t>
+          <t>284765; 340534</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>441921; 766957</t>
+          <t>368728; 415343</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>153937</t>
+          <t>167746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>274357</t>
+          <t>297491</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>428294</t>
+          <t>465238</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>86300; 115591</t>
+          <t>83344; 113074</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>132267; 165477</t>
+          <t>135210; 167913</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>124715; 152932</t>
+          <t>123784; 152225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>140494; 166808</t>
+          <t>154820; 182646</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>170586; 208101</t>
+          <t>168813; 207820</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>231183; 269302</t>
+          <t>232862; 270474</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>205087; 249931</t>
+          <t>205063; 251866</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>259886; 288691</t>
+          <t>280078; 311880</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>263342; 311994</t>
+          <t>263203; 311523</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>377763; 427669</t>
+          <t>377353; 428648</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>339829; 393680</t>
+          <t>341337; 391848</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>408056; 448642</t>
+          <t>444916; 486521</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>621253</t>
+          <t>675270</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>919978</t>
+          <t>781108</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1541231</t>
+          <t>1456378</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>391893; 469366</t>
+          <t>390835; 467759</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>529427; 618780</t>
+          <t>531292; 625083</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>473573; 555243</t>
+          <t>469734; 553028</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>483909; 689114</t>
+          <t>632575; 724668</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>533039; 616523</t>
+          <t>533685; 618416</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>691577; 792112</t>
+          <t>695173; 796731</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>582971; 676205</t>
+          <t>583146; 679166</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>742025; 1477015</t>
+          <t>740525; 822721</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>948521; 1059189</t>
+          <t>934256; 1053357</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1257558; 1382834</t>
+          <t>1256085; 1389061</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1077061; 1201718</t>
+          <t>1083303; 1215326</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1335900; 2124866</t>
+          <t>1398603; 1516704</t>
         </is>
       </c>
     </row>
